--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\04,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE7600E-D96D-45D4-B8C8-C178EC01318A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34434842-2C84-4791-B52C-1A98CABF4A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$133</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -588,22 +580,30 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -1043,7 +1043,8 @@
     <col min="22" max="31" width="6" customWidth="1"/>
     <col min="32" max="32" width="39.85546875" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
-    <col min="34" max="43" width="3" customWidth="1"/>
+    <col min="34" max="34" width="6.85546875" customWidth="1"/>
+    <col min="35" max="43" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -1525,7 +1526,10 @@
         <f>ROUND(G6*S6,0)</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="5"/>
+      <c r="AH6" s="5">
+        <f>(SUM(V6:AE6)+Q6)/11</f>
+        <v>56.722509090909099</v>
+      </c>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5"/>
       <c r="AK6" s="5"/>
@@ -1630,7 +1634,10 @@
         <f t="shared" ref="AG7:AG70" si="7">ROUND(G7*S7,0)</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="5"/>
+      <c r="AH7" s="5">
+        <f t="shared" ref="AH7:AH70" si="8">(SUM(V7:AE7)+Q7)/11</f>
+        <v>156.25216363636363</v>
+      </c>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
       <c r="AK7" s="5"/>
@@ -1734,7 +1741,10 @@
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="AH8" s="5"/>
+      <c r="AH8" s="5">
+        <f t="shared" si="8"/>
+        <v>159.36310909090909</v>
+      </c>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
       <c r="AK8" s="5"/>
@@ -1841,7 +1851,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH9" s="5"/>
+      <c r="AH9" s="5">
+        <f t="shared" si="8"/>
+        <v>1.0181818181818183</v>
+      </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
       <c r="AK9" s="5"/>
@@ -1946,7 +1959,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH10" s="5"/>
+      <c r="AH10" s="5">
+        <f t="shared" si="8"/>
+        <v>60.418181818181807</v>
+      </c>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
       <c r="AK10" s="5"/>
@@ -2051,7 +2067,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="5"/>
+      <c r="AH11" s="5">
+        <f t="shared" si="8"/>
+        <v>81.090909090909093</v>
+      </c>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
       <c r="AK11" s="5"/>
@@ -2146,7 +2165,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="5"/>
+      <c r="AH12" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5"/>
@@ -2204,7 +2226,7 @@
         <v>21.4</v>
       </c>
       <c r="R13" s="4">
-        <f t="shared" ref="R13:R15" si="8">11*Q13-P13-F13-O13</f>
+        <f t="shared" ref="R13:R15" si="9">11*Q13-P13-F13-O13</f>
         <v>2.4000000000000341</v>
       </c>
       <c r="S13" s="4">
@@ -2254,7 +2276,10 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="AH13" s="5"/>
+      <c r="AH13" s="5">
+        <f t="shared" si="8"/>
+        <v>20.254545454545454</v>
+      </c>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
       <c r="AK13" s="5"/>
@@ -2312,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="R14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>64.2</v>
       </c>
       <c r="S14" s="4">
@@ -2362,7 +2387,10 @@
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="AH14" s="5"/>
+      <c r="AH14" s="5">
+        <f t="shared" si="8"/>
+        <v>21.163636363636364</v>
+      </c>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
@@ -2420,7 +2448,7 @@
         <v>76.710000000000008</v>
       </c>
       <c r="R15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.9043200000000979</v>
       </c>
       <c r="S15" s="4">
@@ -2470,7 +2498,10 @@
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="AH15" s="5"/>
+      <c r="AH15" s="5">
+        <f t="shared" si="8"/>
+        <v>70.180999999999997</v>
+      </c>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
       <c r="AK15" s="5"/>
@@ -2577,7 +2608,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="5"/>
+      <c r="AH16" s="5">
+        <f t="shared" si="8"/>
+        <v>335.43781818181827</v>
+      </c>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
       <c r="AK16" s="5"/>
@@ -2635,7 +2669,7 @@
         <v>19.814599999999999</v>
       </c>
       <c r="R17" s="4">
-        <f t="shared" ref="R17:R18" si="9">11*Q17-P17-F17-O17</f>
+        <f t="shared" ref="R17:R18" si="10">11*Q17-P17-F17-O17</f>
         <v>32.752400000000087</v>
       </c>
       <c r="S17" s="4">
@@ -2685,7 +2719,10 @@
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="AH17" s="5"/>
+      <c r="AH17" s="5">
+        <f t="shared" si="8"/>
+        <v>17.220418181818182</v>
+      </c>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
       <c r="AK17" s="5"/>
@@ -2743,7 +2780,7 @@
         <v>11.7798</v>
       </c>
       <c r="R18" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22.27620000000001</v>
       </c>
       <c r="S18" s="4">
@@ -2793,7 +2830,10 @@
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="AH18" s="5"/>
+      <c r="AH18" s="5">
+        <f t="shared" si="8"/>
+        <v>9.2677272727272726</v>
+      </c>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
       <c r="AK18" s="5"/>
@@ -2896,7 +2936,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="5"/>
+      <c r="AH19" s="5">
+        <f t="shared" si="8"/>
+        <v>4.0766</v>
+      </c>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
       <c r="AK19" s="5"/>
@@ -3004,7 +3047,10 @@
         <f t="shared" si="7"/>
         <v>133</v>
       </c>
-      <c r="AH20" s="5"/>
+      <c r="AH20" s="5">
+        <f t="shared" si="8"/>
+        <v>101.16283636363637</v>
+      </c>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
       <c r="AK20" s="5"/>
@@ -3109,7 +3155,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="5"/>
+      <c r="AH21" s="5">
+        <f t="shared" si="8"/>
+        <v>19.942236363636365</v>
+      </c>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
       <c r="AK21" s="5"/>
@@ -3167,7 +3216,7 @@
         <v>42.604799999999997</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" ref="R22:R23" si="10">11*Q22-P22-F22-O22</f>
+        <f t="shared" ref="R22:R23" si="11">11*Q22-P22-F22-O22</f>
         <v>35.592199999999991</v>
       </c>
       <c r="S22" s="4">
@@ -3217,7 +3266,10 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="AH22" s="5"/>
+      <c r="AH22" s="5">
+        <f t="shared" si="8"/>
+        <v>48.698181818181816</v>
+      </c>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
       <c r="AK22" s="5"/>
@@ -3275,7 +3327,7 @@
         <v>4.6915999999999993</v>
       </c>
       <c r="R23" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28.727199999999993</v>
       </c>
       <c r="S23" s="4">
@@ -3325,7 +3377,10 @@
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="AH23" s="5"/>
+      <c r="AH23" s="5">
+        <f t="shared" si="8"/>
+        <v>4.0110363636363635</v>
+      </c>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="5"/>
       <c r="AK23" s="5"/>
@@ -3430,7 +3485,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="5"/>
+      <c r="AH24" s="5">
+        <f t="shared" si="8"/>
+        <v>53.328218181818187</v>
+      </c>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="5"/>
       <c r="AK24" s="5"/>
@@ -3535,7 +3593,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="5"/>
+      <c r="AH25" s="5">
+        <f t="shared" si="8"/>
+        <v>4.8568909090909091</v>
+      </c>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="5"/>
       <c r="AK25" s="5"/>
@@ -3630,7 +3691,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="5"/>
+      <c r="AH26" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="5"/>
       <c r="AK26" s="5"/>
@@ -3738,7 +3802,10 @@
         <f t="shared" si="7"/>
         <v>193</v>
       </c>
-      <c r="AH27" s="5"/>
+      <c r="AH27" s="5">
+        <f t="shared" si="8"/>
+        <v>32.715327272727272</v>
+      </c>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="5"/>
       <c r="AK27" s="5"/>
@@ -3845,7 +3912,10 @@
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="AH28" s="5"/>
+      <c r="AH28" s="5">
+        <f t="shared" si="8"/>
+        <v>64.362636363636369</v>
+      </c>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
       <c r="AK28" s="5"/>
@@ -3952,7 +4022,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH29" s="5"/>
+      <c r="AH29" s="5">
+        <f t="shared" si="8"/>
+        <v>50.255509090909094</v>
+      </c>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5"/>
@@ -4057,7 +4130,10 @@
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH30" s="5"/>
+      <c r="AH30" s="5">
+        <f t="shared" si="8"/>
+        <v>107.99512727272726</v>
+      </c>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="5"/>
       <c r="AK30" s="5"/>
@@ -4158,7 +4234,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="5"/>
+      <c r="AH31" s="5">
+        <f t="shared" si="8"/>
+        <v>1.5492181818181818</v>
+      </c>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
       <c r="AK31" s="5"/>
@@ -4263,7 +4342,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="5"/>
+      <c r="AH32" s="5">
+        <f t="shared" si="8"/>
+        <v>7.6560545454545457</v>
+      </c>
       <c r="AI32" s="5"/>
       <c r="AJ32" s="5"/>
       <c r="AK32" s="5"/>
@@ -4371,7 +4453,10 @@
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="AH33" s="5"/>
+      <c r="AH33" s="5">
+        <f t="shared" si="8"/>
+        <v>16.178872727272729</v>
+      </c>
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
       <c r="AK33" s="5"/>
@@ -4476,7 +4561,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="5"/>
+      <c r="AH34" s="5">
+        <f t="shared" si="8"/>
+        <v>10.815036363636363</v>
+      </c>
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
       <c r="AK34" s="5"/>
@@ -4581,7 +4669,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="5"/>
+      <c r="AH35" s="5">
+        <f t="shared" si="8"/>
+        <v>10.997036363636365</v>
+      </c>
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
       <c r="AK35" s="5"/>
@@ -4688,7 +4779,10 @@
         <f t="shared" si="7"/>
         <v>160</v>
       </c>
-      <c r="AH36" s="5"/>
+      <c r="AH36" s="5">
+        <f t="shared" si="8"/>
+        <v>236.15636363636366</v>
+      </c>
       <c r="AI36" s="5"/>
       <c r="AJ36" s="5"/>
       <c r="AK36" s="5"/>
@@ -4793,7 +4887,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="5"/>
+      <c r="AH37" s="5">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
       <c r="AK37" s="5"/>
@@ -4837,7 +4934,7 @@
         <v>332</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
         <v>-233</v>
       </c>
       <c r="M38" s="5"/>
@@ -4847,7 +4944,7 @@
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5">
-        <f t="shared" ref="Q38:Q69" si="12">E38/5</f>
+        <f t="shared" ref="Q38:Q69" si="13">E38/5</f>
         <v>19.8</v>
       </c>
       <c r="R38" s="4"/>
@@ -4860,7 +4957,7 @@
         <v>15.959595959595958</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" ref="U38:U69" si="13">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="U38:U69" si="14">(F38+O38+P38)/Q38</f>
         <v>15.959595959595958</v>
       </c>
       <c r="V38" s="5">
@@ -4898,7 +4995,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="5"/>
+      <c r="AH38" s="5">
+        <f t="shared" si="8"/>
+        <v>52.709090909090904</v>
+      </c>
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
       <c r="AK38" s="5"/>
@@ -4942,7 +5042,7 @@
         <v>62</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-31</v>
       </c>
       <c r="M39" s="5"/>
@@ -4952,7 +5052,7 @@
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.2</v>
       </c>
       <c r="R39" s="4"/>
@@ -4965,7 +5065,7 @@
         <v>14.193548387096774</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.193548387096774</v>
       </c>
       <c r="V39" s="5">
@@ -5003,7 +5103,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="5"/>
+      <c r="AH39" s="5">
+        <f t="shared" si="8"/>
+        <v>7.745454545454546</v>
+      </c>
       <c r="AI39" s="5"/>
       <c r="AJ39" s="5"/>
       <c r="AK39" s="5"/>
@@ -5045,7 +5148,7 @@
         <v>20.2</v>
       </c>
       <c r="L40" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.9329999999999998</v>
       </c>
       <c r="M40" s="5"/>
@@ -5055,7 +5158,7 @@
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.0533999999999999</v>
       </c>
       <c r="R40" s="4">
@@ -5071,7 +5174,7 @@
         <v>11</v>
       </c>
       <c r="U40" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.21164897243596</v>
       </c>
       <c r="V40" s="5">
@@ -5111,7 +5214,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AH40" s="5"/>
+      <c r="AH40" s="5">
+        <f t="shared" si="8"/>
+        <v>2.9330363636363641</v>
+      </c>
       <c r="AI40" s="5"/>
       <c r="AJ40" s="5"/>
       <c r="AK40" s="5"/>
@@ -5155,7 +5261,7 @@
         <v>270</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>51</v>
       </c>
       <c r="M41" s="5"/>
@@ -5165,7 +5271,7 @@
       </c>
       <c r="P41" s="5"/>
       <c r="Q41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>64.2</v>
       </c>
       <c r="R41" s="4"/>
@@ -5178,7 +5284,7 @@
         <v>17.024922118380061</v>
       </c>
       <c r="U41" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17.024922118380061</v>
       </c>
       <c r="V41" s="5">
@@ -5216,7 +5322,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="5"/>
+      <c r="AH41" s="5">
+        <f t="shared" si="8"/>
+        <v>67.654545454545456</v>
+      </c>
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
       <c r="AK41" s="5"/>
@@ -5260,7 +5369,7 @@
         <v>10</v>
       </c>
       <c r="L42" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-25</v>
       </c>
       <c r="M42" s="5"/>
@@ -5270,7 +5379,7 @@
       </c>
       <c r="P42" s="5"/>
       <c r="Q42" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="R42" s="4"/>
@@ -5283,7 +5392,7 @@
         <v>-11.333333333333334</v>
       </c>
       <c r="U42" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-11.333333333333334</v>
       </c>
       <c r="V42" s="5">
@@ -5321,7 +5430,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH42" s="5"/>
+      <c r="AH42" s="5">
+        <f t="shared" si="8"/>
+        <v>29.25454545454545</v>
+      </c>
       <c r="AI42" s="5"/>
       <c r="AJ42" s="5"/>
       <c r="AK42" s="5"/>
@@ -5365,7 +5477,7 @@
         <v>117.2</v>
       </c>
       <c r="L43" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-10.221000000000004</v>
       </c>
       <c r="M43" s="5"/>
@@ -5375,7 +5487,7 @@
       </c>
       <c r="P43" s="5"/>
       <c r="Q43" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.395800000000001</v>
       </c>
       <c r="R43" s="4"/>
@@ -5388,7 +5500,7 @@
         <v>11.357359855672607</v>
       </c>
       <c r="U43" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.357359855672607</v>
       </c>
       <c r="V43" s="5">
@@ -5426,7 +5538,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="5"/>
+      <c r="AH43" s="5">
+        <f t="shared" si="8"/>
+        <v>21.199436363636366</v>
+      </c>
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
       <c r="AK43" s="5"/>
@@ -5470,7 +5585,7 @@
         <v>92</v>
       </c>
       <c r="L44" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-87</v>
       </c>
       <c r="M44" s="5"/>
@@ -5480,7 +5595,7 @@
       </c>
       <c r="P44" s="5"/>
       <c r="Q44" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R44" s="17">
@@ -5495,7 +5610,7 @@
         <v>109</v>
       </c>
       <c r="U44" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>89</v>
       </c>
       <c r="V44" s="5">
@@ -5533,7 +5648,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="AH44" s="5"/>
+      <c r="AH44" s="5">
+        <f t="shared" si="8"/>
+        <v>13.854545454545455</v>
+      </c>
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
       <c r="AK44" s="5"/>
@@ -5577,7 +5695,7 @@
         <v>136</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-124</v>
       </c>
       <c r="M45" s="5"/>
@@ -5587,7 +5705,7 @@
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4</v>
       </c>
       <c r="R45" s="4"/>
@@ -5600,7 +5718,7 @@
         <v>105</v>
       </c>
       <c r="U45" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>105</v>
       </c>
       <c r="V45" s="5">
@@ -5638,7 +5756,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="5"/>
+      <c r="AH45" s="5">
+        <f t="shared" si="8"/>
+        <v>20.509090909090911</v>
+      </c>
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
       <c r="AK45" s="5"/>
@@ -5680,7 +5801,7 @@
         <v>44.1</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-43.361000000000004</v>
       </c>
       <c r="M46" s="10"/>
@@ -5690,7 +5811,7 @@
       </c>
       <c r="P46" s="10"/>
       <c r="Q46" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14779999999999999</v>
       </c>
       <c r="R46" s="12"/>
@@ -5703,7 +5824,7 @@
         <v>24.560216508795673</v>
       </c>
       <c r="U46" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.560216508795673</v>
       </c>
       <c r="V46" s="10">
@@ -5741,7 +5862,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH46" s="5"/>
+      <c r="AH46" s="5">
+        <f t="shared" si="8"/>
+        <v>10.217563636363638</v>
+      </c>
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
       <c r="AK46" s="5"/>
@@ -5785,7 +5909,7 @@
         <v>114.8</v>
       </c>
       <c r="L47" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-16.795999999999992</v>
       </c>
       <c r="M47" s="5"/>
@@ -5795,7 +5919,7 @@
       </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19.6008</v>
       </c>
       <c r="R47" s="4"/>
@@ -5808,7 +5932,7 @@
         <v>12.649187788253542</v>
       </c>
       <c r="U47" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.649187788253542</v>
       </c>
       <c r="V47" s="5">
@@ -5846,7 +5970,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH47" s="5"/>
+      <c r="AH47" s="5">
+        <f t="shared" si="8"/>
+        <v>24.241018181818177</v>
+      </c>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
       <c r="AK47" s="5"/>
@@ -5890,7 +6017,7 @@
         <v>287</v>
       </c>
       <c r="L48" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-146</v>
       </c>
       <c r="M48" s="5"/>
@@ -5900,7 +6027,7 @@
       </c>
       <c r="P48" s="5"/>
       <c r="Q48" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28.2</v>
       </c>
       <c r="R48" s="4"/>
@@ -5913,7 +6040,7 @@
         <v>36.028368794326241</v>
       </c>
       <c r="U48" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36.028368794326241</v>
       </c>
       <c r="V48" s="5">
@@ -5951,7 +6078,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH48" s="5"/>
+      <c r="AH48" s="5">
+        <f t="shared" si="8"/>
+        <v>76.761818181818185</v>
+      </c>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
       <c r="AK48" s="5"/>
@@ -5995,7 +6125,7 @@
         <v>244</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-246</v>
       </c>
       <c r="M49" s="5"/>
@@ -6005,7 +6135,7 @@
       </c>
       <c r="P49" s="5"/>
       <c r="Q49" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
       <c r="R49" s="17">
@@ -6020,7 +6150,7 @@
         <v>-1142.5</v>
       </c>
       <c r="U49" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-892.5</v>
       </c>
       <c r="V49" s="5">
@@ -6058,7 +6188,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AH49" s="5"/>
+      <c r="AH49" s="5">
+        <f t="shared" si="8"/>
+        <v>41.836363636363643</v>
+      </c>
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
       <c r="AK49" s="5"/>
@@ -6102,7 +6235,7 @@
         <v>42</v>
       </c>
       <c r="L50" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1460000000000008</v>
       </c>
       <c r="M50" s="5"/>
@@ -6112,7 +6245,7 @@
       </c>
       <c r="P50" s="5"/>
       <c r="Q50" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.6292000000000009</v>
       </c>
       <c r="R50" s="4"/>
@@ -6125,7 +6258,7 @@
         <v>20.847726324572381</v>
       </c>
       <c r="U50" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.847726324572381</v>
       </c>
       <c r="V50" s="5">
@@ -6163,7 +6296,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="5"/>
+      <c r="AH50" s="5">
+        <f t="shared" si="8"/>
+        <v>8.1425818181818173</v>
+      </c>
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
       <c r="AK50" s="5"/>
@@ -6207,7 +6343,7 @@
         <v>121.4</v>
       </c>
       <c r="L51" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13.73399999999998</v>
       </c>
       <c r="M51" s="5"/>
@@ -6217,11 +6353,11 @@
       </c>
       <c r="P51" s="5"/>
       <c r="Q51" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27.026799999999998</v>
       </c>
       <c r="R51" s="4">
-        <f t="shared" ref="R51:R53" si="14">11*Q51-P51-F51-O51</f>
+        <f t="shared" ref="R51:R53" si="15">11*Q51-P51-F51-O51</f>
         <v>41.447799999999944</v>
       </c>
       <c r="S51" s="4">
@@ -6233,7 +6369,7 @@
         <v>10.999999999999998</v>
       </c>
       <c r="U51" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.4664185179155513</v>
       </c>
       <c r="V51" s="5">
@@ -6271,7 +6407,10 @@
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
-      <c r="AH51" s="5"/>
+      <c r="AH51" s="5">
+        <f t="shared" si="8"/>
+        <v>24.143200000000004</v>
+      </c>
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
       <c r="AK51" s="5"/>
@@ -6315,7 +6454,7 @@
         <v>40.4</v>
       </c>
       <c r="L52" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-12.032</v>
       </c>
       <c r="M52" s="5"/>
@@ -6325,11 +6464,11 @@
       </c>
       <c r="P52" s="5"/>
       <c r="Q52" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.6735999999999995</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>35.794600000000003</v>
       </c>
       <c r="S52" s="4">
@@ -6341,7 +6480,7 @@
         <v>11</v>
       </c>
       <c r="U52" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.691025098702764</v>
       </c>
       <c r="V52" s="5">
@@ -6379,7 +6518,10 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="AH52" s="5"/>
+      <c r="AH52" s="5">
+        <f t="shared" si="8"/>
+        <v>7.1843272727272725</v>
+      </c>
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
       <c r="AK52" s="5"/>
@@ -6423,7 +6565,7 @@
         <v>132</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5</v>
       </c>
       <c r="M53" s="5"/>
@@ -6433,11 +6575,11 @@
       </c>
       <c r="P53" s="5"/>
       <c r="Q53" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>25.4</v>
       </c>
       <c r="R53" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.0000000000000284</v>
       </c>
       <c r="S53" s="4">
@@ -6449,7 +6591,7 @@
         <v>11</v>
       </c>
       <c r="U53" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.724409448818898</v>
       </c>
       <c r="V53" s="5">
@@ -6487,7 +6629,10 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="AH53" s="5"/>
+      <c r="AH53" s="5">
+        <f t="shared" si="8"/>
+        <v>23.763636363636365</v>
+      </c>
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
       <c r="AK53" s="5"/>
@@ -6531,7 +6676,7 @@
         <v>169</v>
       </c>
       <c r="L54" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8</v>
       </c>
       <c r="M54" s="5"/>
@@ -6541,7 +6686,7 @@
       </c>
       <c r="P54" s="5"/>
       <c r="Q54" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32.200000000000003</v>
       </c>
       <c r="R54" s="4"/>
@@ -6554,7 +6699,7 @@
         <v>20.186335403726705</v>
       </c>
       <c r="U54" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.186335403726705</v>
       </c>
       <c r="V54" s="5">
@@ -6592,7 +6737,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="5"/>
+      <c r="AH54" s="5">
+        <f t="shared" si="8"/>
+        <v>40.527272727272731</v>
+      </c>
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
       <c r="AK54" s="5"/>
@@ -6636,7 +6784,7 @@
         <v>126</v>
       </c>
       <c r="L55" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-20</v>
       </c>
       <c r="M55" s="5"/>
@@ -6646,7 +6794,7 @@
       </c>
       <c r="P55" s="5"/>
       <c r="Q55" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.2</v>
       </c>
       <c r="R55" s="4">
@@ -6662,7 +6810,7 @@
         <v>11</v>
       </c>
       <c r="U55" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.5283018867924536</v>
       </c>
       <c r="V55" s="5">
@@ -6700,7 +6848,10 @@
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AH55" s="5"/>
+      <c r="AH55" s="5">
+        <f t="shared" si="8"/>
+        <v>18.799999999999997</v>
+      </c>
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
       <c r="AK55" s="5"/>
@@ -6744,7 +6895,7 @@
         <v>141</v>
       </c>
       <c r="L56" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-77</v>
       </c>
       <c r="M56" s="5"/>
@@ -6754,7 +6905,7 @@
       </c>
       <c r="P56" s="5"/>
       <c r="Q56" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.8</v>
       </c>
       <c r="R56" s="17">
@@ -6769,7 +6920,7 @@
         <v>18.4375</v>
       </c>
       <c r="U56" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.53125</v>
       </c>
       <c r="V56" s="5">
@@ -6807,7 +6958,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AH56" s="5"/>
+      <c r="AH56" s="5">
+        <f t="shared" si="8"/>
+        <v>12.527272727272729</v>
+      </c>
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
       <c r="AK56" s="5"/>
@@ -6851,7 +7005,7 @@
         <v>103.4</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.9599999999999937</v>
       </c>
       <c r="M57" s="5"/>
@@ -6861,11 +7015,11 @@
       </c>
       <c r="P57" s="5"/>
       <c r="Q57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.672000000000001</v>
       </c>
       <c r="R57" s="4">
-        <f t="shared" ref="R57:R60" si="15">11*Q57-P57-F57-O57</f>
+        <f t="shared" ref="R57:R60" si="16">11*Q57-P57-F57-O57</f>
         <v>18.171999999999997</v>
       </c>
       <c r="S57" s="4">
@@ -6877,7 +7031,7 @@
         <v>11</v>
       </c>
       <c r="U57" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.161498708010335</v>
       </c>
       <c r="V57" s="5">
@@ -6915,7 +7069,10 @@
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="AH57" s="5"/>
+      <c r="AH57" s="5">
+        <f t="shared" si="8"/>
+        <v>21.195436363636361</v>
+      </c>
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
       <c r="AK57" s="5"/>
@@ -6959,7 +7116,7 @@
         <v>228</v>
       </c>
       <c r="L58" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>37</v>
       </c>
       <c r="M58" s="5"/>
@@ -6969,11 +7126,11 @@
       </c>
       <c r="P58" s="5"/>
       <c r="Q58" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>53</v>
       </c>
       <c r="R58" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>147.00000000000011</v>
       </c>
       <c r="S58" s="4">
@@ -6985,7 +7142,7 @@
         <v>11</v>
       </c>
       <c r="U58" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.2264150943396199</v>
       </c>
       <c r="V58" s="5">
@@ -7023,7 +7180,10 @@
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="AH58" s="5"/>
+      <c r="AH58" s="5">
+        <f t="shared" si="8"/>
+        <v>41.345454545454544</v>
+      </c>
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
       <c r="AK58" s="5"/>
@@ -7067,7 +7227,7 @@
         <v>74.150000000000006</v>
       </c>
       <c r="L59" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.025999999999996</v>
       </c>
       <c r="M59" s="5"/>
@@ -7077,7 +7237,7 @@
       </c>
       <c r="P59" s="5"/>
       <c r="Q59" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.8352</v>
       </c>
       <c r="R59" s="4"/>
@@ -7090,7 +7250,7 @@
         <v>11.169276278274092</v>
       </c>
       <c r="U59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.169276278274092</v>
       </c>
       <c r="V59" s="5">
@@ -7128,7 +7288,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH59" s="5"/>
+      <c r="AH59" s="5">
+        <f t="shared" si="8"/>
+        <v>17.398545454545456</v>
+      </c>
       <c r="AI59" s="5"/>
       <c r="AJ59" s="5"/>
       <c r="AK59" s="5"/>
@@ -7172,7 +7335,7 @@
         <v>38.4</v>
       </c>
       <c r="L60" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8.5999999999998522E-2</v>
       </c>
       <c r="M60" s="5"/>
@@ -7182,11 +7345,11 @@
       </c>
       <c r="P60" s="5"/>
       <c r="Q60" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.6627999999999998</v>
       </c>
       <c r="R60" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.9913999999999987</v>
       </c>
       <c r="S60" s="4">
@@ -7198,7 +7361,7 @@
         <v>11</v>
       </c>
       <c r="U60" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.740121104557081</v>
       </c>
       <c r="V60" s="5">
@@ -7236,7 +7399,10 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AH60" s="5"/>
+      <c r="AH60" s="5">
+        <f t="shared" si="8"/>
+        <v>4.6907636363636369</v>
+      </c>
       <c r="AI60" s="5"/>
       <c r="AJ60" s="5"/>
       <c r="AK60" s="5"/>
@@ -7280,7 +7446,7 @@
         <v>179</v>
       </c>
       <c r="L61" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="M61" s="5"/>
@@ -7290,7 +7456,7 @@
       </c>
       <c r="P61" s="5"/>
       <c r="Q61" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39</v>
       </c>
       <c r="R61" s="4"/>
@@ -7303,7 +7469,7 @@
         <v>13.892307692307694</v>
       </c>
       <c r="U61" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.892307692307694</v>
       </c>
       <c r="V61" s="5">
@@ -7341,7 +7507,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="5"/>
+      <c r="AH61" s="5">
+        <f t="shared" si="8"/>
+        <v>42.090909090909093</v>
+      </c>
       <c r="AI61" s="5"/>
       <c r="AJ61" s="5"/>
       <c r="AK61" s="5"/>
@@ -7385,7 +7554,7 @@
         <v>23</v>
       </c>
       <c r="L62" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3</v>
       </c>
       <c r="M62" s="5"/>
@@ -7395,7 +7564,7 @@
       </c>
       <c r="P62" s="5"/>
       <c r="Q62" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="R62" s="4"/>
@@ -7408,7 +7577,7 @@
         <v>27</v>
       </c>
       <c r="U62" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>27</v>
       </c>
       <c r="V62" s="5">
@@ -7448,7 +7617,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH62" s="5"/>
+      <c r="AH62" s="5">
+        <f t="shared" si="8"/>
+        <v>4.8545454545454545</v>
+      </c>
       <c r="AI62" s="5"/>
       <c r="AJ62" s="5"/>
       <c r="AK62" s="5"/>
@@ -7492,7 +7664,7 @@
         <v>43.8</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6.019999999999996</v>
       </c>
       <c r="M63" s="5"/>
@@ -7502,11 +7674,11 @@
       </c>
       <c r="P63" s="5"/>
       <c r="Q63" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.556</v>
       </c>
       <c r="R63" s="4">
-        <f t="shared" ref="R63:R64" si="16">11*Q63-P63-F63-O63</f>
+        <f t="shared" ref="R63:R64" si="17">11*Q63-P63-F63-O63</f>
         <v>15.325000000000003</v>
       </c>
       <c r="S63" s="4">
@@ -7518,7 +7690,7 @@
         <v>11</v>
       </c>
       <c r="U63" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.9718104817363677</v>
       </c>
       <c r="V63" s="5">
@@ -7558,7 +7730,10 @@
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="AH63" s="5"/>
+      <c r="AH63" s="5">
+        <f t="shared" si="8"/>
+        <v>2.6069636363636364</v>
+      </c>
       <c r="AI63" s="5"/>
       <c r="AJ63" s="5"/>
       <c r="AK63" s="5"/>
@@ -7602,7 +7777,7 @@
         <v>78.8</v>
       </c>
       <c r="L64" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3.4669999999999987</v>
       </c>
       <c r="M64" s="5"/>
@@ -7612,11 +7787,11 @@
       </c>
       <c r="P64" s="5"/>
       <c r="Q64" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.066599999999999</v>
       </c>
       <c r="R64" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>76.991600000000005</v>
       </c>
       <c r="S64" s="4">
@@ -7628,7 +7803,7 @@
         <v>11</v>
       </c>
       <c r="U64" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.8899154421037263</v>
       </c>
       <c r="V64" s="5">
@@ -7668,7 +7843,10 @@
         <f t="shared" si="7"/>
         <v>77</v>
       </c>
-      <c r="AH64" s="5"/>
+      <c r="AH64" s="5">
+        <f t="shared" si="8"/>
+        <v>6.4128909090909101</v>
+      </c>
       <c r="AI64" s="5"/>
       <c r="AJ64" s="5"/>
       <c r="AK64" s="5"/>
@@ -7712,7 +7890,7 @@
         <v>569</v>
       </c>
       <c r="L65" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-498</v>
       </c>
       <c r="M65" s="5"/>
@@ -7722,7 +7900,7 @@
       </c>
       <c r="P65" s="5"/>
       <c r="Q65" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.2</v>
       </c>
       <c r="R65" s="4"/>
@@ -7735,7 +7913,7 @@
         <v>42.323943661971832</v>
       </c>
       <c r="U65" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42.323943661971832</v>
       </c>
       <c r="V65" s="5">
@@ -7775,7 +7953,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH65" s="5"/>
+      <c r="AH65" s="5">
+        <f t="shared" si="8"/>
+        <v>66.981818181818184</v>
+      </c>
       <c r="AI65" s="5"/>
       <c r="AJ65" s="5"/>
       <c r="AK65" s="5"/>
@@ -7817,7 +7998,7 @@
         <v>272</v>
       </c>
       <c r="L66" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-272</v>
       </c>
       <c r="M66" s="5"/>
@@ -7827,7 +8008,7 @@
       </c>
       <c r="P66" s="5"/>
       <c r="Q66" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R66" s="17">
@@ -7842,7 +8023,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U66" s="5" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V66" s="5">
@@ -7880,7 +8061,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AH66" s="5"/>
+      <c r="AH66" s="5">
+        <f t="shared" si="8"/>
+        <v>51.81818181818182</v>
+      </c>
       <c r="AI66" s="5"/>
       <c r="AJ66" s="5"/>
       <c r="AK66" s="5"/>
@@ -7924,7 +8108,7 @@
         <v>144.19999999999999</v>
       </c>
       <c r="L67" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.257000000000005</v>
       </c>
       <c r="M67" s="5"/>
@@ -7934,7 +8118,7 @@
       </c>
       <c r="P67" s="5"/>
       <c r="Q67" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30.891399999999997</v>
       </c>
       <c r="R67" s="4"/>
@@ -7947,7 +8131,7 @@
         <v>13.417676116977539</v>
       </c>
       <c r="U67" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.417676116977539</v>
       </c>
       <c r="V67" s="5">
@@ -7985,7 +8169,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH67" s="5"/>
+      <c r="AH67" s="5">
+        <f t="shared" si="8"/>
+        <v>26.931236363636355</v>
+      </c>
       <c r="AI67" s="5"/>
       <c r="AJ67" s="5"/>
       <c r="AK67" s="5"/>
@@ -8029,7 +8216,7 @@
         <v>184.2</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-11.531999999999982</v>
       </c>
       <c r="M68" s="5"/>
@@ -8039,11 +8226,11 @@
       </c>
       <c r="P68" s="5"/>
       <c r="Q68" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34.5336</v>
       </c>
       <c r="R68" s="4">
-        <f t="shared" ref="R68:R70" si="17">11*Q68-P68-F68-O68</f>
+        <f t="shared" ref="R68:R70" si="18">11*Q68-P68-F68-O68</f>
         <v>32.209119999999871</v>
       </c>
       <c r="S68" s="4">
@@ -8055,7 +8242,7 @@
         <v>11</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.067310677137632</v>
       </c>
       <c r="V68" s="5">
@@ -8093,7 +8280,10 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AH68" s="5"/>
+      <c r="AH68" s="5">
+        <f t="shared" si="8"/>
+        <v>29.374563636363636</v>
+      </c>
       <c r="AI68" s="5"/>
       <c r="AJ68" s="5"/>
       <c r="AK68" s="5"/>
@@ -8137,7 +8327,7 @@
         <v>345.4</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6.9759999999999991</v>
       </c>
       <c r="M69" s="5"/>
@@ -8147,11 +8337,11 @@
       </c>
       <c r="P69" s="5"/>
       <c r="Q69" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>67.684799999999996</v>
       </c>
       <c r="R69" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>46.599290000000167</v>
       </c>
       <c r="S69" s="4">
@@ -8163,7 +8353,7 @@
         <v>11</v>
       </c>
       <c r="U69" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.311525039595299</v>
       </c>
       <c r="V69" s="5">
@@ -8201,7 +8391,10 @@
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
-      <c r="AH69" s="5"/>
+      <c r="AH69" s="5">
+        <f t="shared" si="8"/>
+        <v>78.235072727272723</v>
+      </c>
       <c r="AI69" s="5"/>
       <c r="AJ69" s="5"/>
       <c r="AK69" s="5"/>
@@ -8245,7 +8438,7 @@
         <v>128.9</v>
       </c>
       <c r="L70" s="5">
-        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
         <v>15.281000000000006</v>
       </c>
       <c r="M70" s="5"/>
@@ -8255,11 +8448,11 @@
       </c>
       <c r="P70" s="5"/>
       <c r="Q70" s="5">
-        <f t="shared" ref="Q70:Q101" si="19">E70/5</f>
+        <f t="shared" ref="Q70:Q101" si="20">E70/5</f>
         <v>28.836200000000002</v>
       </c>
       <c r="R70" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.3116000000001407</v>
       </c>
       <c r="S70" s="4">
@@ -8271,7 +8464,7 @@
         <v>11</v>
       </c>
       <c r="U70" s="5">
-        <f t="shared" ref="U70:U101" si="20">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="U70:U101" si="21">(F70+O70+P70)/Q70</f>
         <v>10.885158238602864</v>
       </c>
       <c r="V70" s="5">
@@ -8309,7 +8502,10 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="AH70" s="5"/>
+      <c r="AH70" s="5">
+        <f t="shared" si="8"/>
+        <v>28.597381818181816</v>
+      </c>
       <c r="AI70" s="5"/>
       <c r="AJ70" s="5"/>
       <c r="AK70" s="5"/>
@@ -8351,7 +8547,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="L71" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.9999999999999645E-2</v>
       </c>
       <c r="M71" s="5"/>
@@ -8361,20 +8557,20 @@
       </c>
       <c r="P71" s="5"/>
       <c r="Q71" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="R71" s="4"/>
       <c r="S71" s="4">
-        <f t="shared" ref="S71:S133" si="21">R71</f>
+        <f t="shared" ref="S71:S133" si="22">R71</f>
         <v>0</v>
       </c>
       <c r="T71" s="5">
-        <f t="shared" ref="T71:T133" si="22">(F71+O71+P71+S71)/Q71</f>
+        <f t="shared" ref="T71:T133" si="23">(F71+O71+P71+S71)/Q71</f>
         <v>62</v>
       </c>
       <c r="U71" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>62</v>
       </c>
       <c r="V71" s="5">
@@ -8411,10 +8607,13 @@
         <v>102</v>
       </c>
       <c r="AG71" s="5">
-        <f t="shared" ref="AG71:AG133" si="23">ROUND(G71*S71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH71" s="5"/>
+        <f t="shared" ref="AG71:AG133" si="24">ROUND(G71*S71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH71" s="5">
+        <f t="shared" ref="AH71:AH133" si="25">(SUM(V71:AE71)+Q71)/11</f>
+        <v>2.3818181818181818</v>
+      </c>
       <c r="AI71" s="5"/>
       <c r="AJ71" s="5"/>
       <c r="AK71" s="5"/>
@@ -8458,7 +8657,7 @@
         <v>274.7</v>
       </c>
       <c r="L72" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-194.08599999999998</v>
       </c>
       <c r="M72" s="5"/>
@@ -8468,20 +8667,20 @@
       </c>
       <c r="P72" s="5"/>
       <c r="Q72" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.122800000000002</v>
       </c>
       <c r="R72" s="4"/>
       <c r="S72" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T72" s="5">
+        <f t="shared" si="23"/>
+        <v>27.751507182375267</v>
+      </c>
+      <c r="U72" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T72" s="5">
-        <f t="shared" si="22"/>
-        <v>27.751507182375267</v>
-      </c>
-      <c r="U72" s="5">
-        <f t="shared" si="20"/>
         <v>27.751507182375267</v>
       </c>
       <c r="V72" s="5">
@@ -8516,10 +8715,13 @@
       </c>
       <c r="AF72" s="5"/>
       <c r="AG72" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH72" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="5">
+        <f t="shared" si="25"/>
+        <v>59.137054545454539</v>
+      </c>
       <c r="AI72" s="5"/>
       <c r="AJ72" s="5"/>
       <c r="AK72" s="5"/>
@@ -8551,7 +8753,7 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M73" s="10"/>
@@ -8561,20 +8763,20 @@
       </c>
       <c r="P73" s="10"/>
       <c r="Q73" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R73" s="12"/>
       <c r="S73" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T73" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U73" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T73" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U73" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" s="10">
@@ -8611,10 +8813,13 @@
         <v>46</v>
       </c>
       <c r="AG73" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH73" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH73" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI73" s="5"/>
       <c r="AJ73" s="5"/>
       <c r="AK73" s="5"/>
@@ -8658,7 +8863,7 @@
         <v>55</v>
       </c>
       <c r="L74" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12</v>
       </c>
       <c r="M74" s="5"/>
@@ -8668,20 +8873,20 @@
       </c>
       <c r="P74" s="5"/>
       <c r="Q74" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.4</v>
       </c>
       <c r="R74" s="4"/>
       <c r="S74" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T74" s="5">
+        <f t="shared" si="23"/>
+        <v>16.865671641791046</v>
+      </c>
+      <c r="U74" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T74" s="5">
-        <f t="shared" si="22"/>
-        <v>16.865671641791046</v>
-      </c>
-      <c r="U74" s="5">
-        <f t="shared" si="20"/>
         <v>16.865671641791046</v>
       </c>
       <c r="V74" s="5">
@@ -8716,10 +8921,13 @@
       </c>
       <c r="AF74" s="5"/>
       <c r="AG74" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH74" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH74" s="5">
+        <f t="shared" si="25"/>
+        <v>11.945454545454544</v>
+      </c>
       <c r="AI74" s="5"/>
       <c r="AJ74" s="5"/>
       <c r="AK74" s="5"/>
@@ -8763,7 +8971,7 @@
         <v>55</v>
       </c>
       <c r="L75" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-6</v>
       </c>
       <c r="M75" s="5"/>
@@ -8773,20 +8981,20 @@
       </c>
       <c r="P75" s="5"/>
       <c r="Q75" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="R75" s="4"/>
       <c r="S75" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T75" s="5">
+        <f t="shared" si="23"/>
+        <v>20.204081632653065</v>
+      </c>
+      <c r="U75" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T75" s="5">
-        <f t="shared" si="22"/>
-        <v>20.204081632653065</v>
-      </c>
-      <c r="U75" s="5">
-        <f t="shared" si="20"/>
         <v>20.204081632653065</v>
       </c>
       <c r="V75" s="5">
@@ -8823,10 +9031,13 @@
         <v>175</v>
       </c>
       <c r="AG75" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH75" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH75" s="5">
+        <f t="shared" si="25"/>
+        <v>19.727272727272723</v>
+      </c>
       <c r="AI75" s="5"/>
       <c r="AJ75" s="5"/>
       <c r="AK75" s="5"/>
@@ -8870,7 +9081,7 @@
         <v>118</v>
       </c>
       <c r="L76" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="M76" s="5"/>
@@ -8880,23 +9091,23 @@
       </c>
       <c r="P76" s="5"/>
       <c r="Q76" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>26.6</v>
       </c>
       <c r="R76" s="4">
-        <f t="shared" ref="R76" si="24">11*Q76-P76-F76-O76</f>
+        <f t="shared" ref="R76" si="26">11*Q76-P76-F76-O76</f>
         <v>35.600000000000023</v>
       </c>
       <c r="S76" s="4">
+        <f t="shared" si="22"/>
+        <v>35.600000000000023</v>
+      </c>
+      <c r="T76" s="5">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="U76" s="5">
         <f t="shared" si="21"/>
-        <v>35.600000000000023</v>
-      </c>
-      <c r="T76" s="5">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="U76" s="5">
-        <f t="shared" si="20"/>
         <v>9.6616541353383454</v>
       </c>
       <c r="V76" s="5">
@@ -8931,10 +9142,13 @@
       </c>
       <c r="AF76" s="5"/>
       <c r="AG76" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
-      <c r="AH76" s="5"/>
+      <c r="AH76" s="5">
+        <f t="shared" si="25"/>
+        <v>27.181818181818187</v>
+      </c>
       <c r="AI76" s="5"/>
       <c r="AJ76" s="5"/>
       <c r="AK76" s="5"/>
@@ -8978,7 +9192,7 @@
         <v>55</v>
       </c>
       <c r="L77" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M77" s="5"/>
@@ -8988,20 +9202,20 @@
       </c>
       <c r="P77" s="5"/>
       <c r="Q77" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="R77" s="4"/>
       <c r="S77" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T77" s="5">
+        <f t="shared" si="23"/>
+        <v>15.927272727272726</v>
+      </c>
+      <c r="U77" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T77" s="5">
-        <f t="shared" si="22"/>
-        <v>15.927272727272726</v>
-      </c>
-      <c r="U77" s="5">
-        <f t="shared" si="20"/>
         <v>15.927272727272726</v>
       </c>
       <c r="V77" s="5">
@@ -9036,10 +9250,13 @@
       </c>
       <c r="AF77" s="5"/>
       <c r="AG77" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH77" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH77" s="5">
+        <f t="shared" si="25"/>
+        <v>14.563636363636364</v>
+      </c>
       <c r="AI77" s="5"/>
       <c r="AJ77" s="5"/>
       <c r="AK77" s="5"/>
@@ -9083,7 +9300,7 @@
         <v>134</v>
       </c>
       <c r="L78" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-4</v>
       </c>
       <c r="M78" s="5"/>
@@ -9093,20 +9310,20 @@
       </c>
       <c r="P78" s="5"/>
       <c r="Q78" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R78" s="4"/>
       <c r="S78" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T78" s="5">
+        <f t="shared" si="23"/>
+        <v>14.746153846153845</v>
+      </c>
+      <c r="U78" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T78" s="5">
-        <f t="shared" si="22"/>
-        <v>14.746153846153845</v>
-      </c>
-      <c r="U78" s="5">
-        <f t="shared" si="20"/>
         <v>14.746153846153845</v>
       </c>
       <c r="V78" s="5">
@@ -9141,10 +9358,13 @@
       </c>
       <c r="AF78" s="5"/>
       <c r="AG78" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH78" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH78" s="5">
+        <f t="shared" si="25"/>
+        <v>32.400000000000006</v>
+      </c>
       <c r="AI78" s="5"/>
       <c r="AJ78" s="5"/>
       <c r="AK78" s="5"/>
@@ -9176,7 +9396,7 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M79" s="10"/>
@@ -9186,20 +9406,20 @@
       </c>
       <c r="P79" s="10"/>
       <c r="Q79" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R79" s="12"/>
       <c r="S79" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T79" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U79" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T79" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U79" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" s="10">
@@ -9236,10 +9456,13 @@
         <v>46</v>
       </c>
       <c r="AG79" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH79" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH79" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI79" s="5"/>
       <c r="AJ79" s="5"/>
       <c r="AK79" s="5"/>
@@ -9283,7 +9506,7 @@
         <v>40</v>
       </c>
       <c r="L80" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-12</v>
       </c>
       <c r="M80" s="5"/>
@@ -9293,20 +9516,20 @@
       </c>
       <c r="P80" s="5"/>
       <c r="Q80" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.6</v>
       </c>
       <c r="R80" s="4"/>
       <c r="S80" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T80" s="5">
+        <f t="shared" si="23"/>
+        <v>12.5</v>
+      </c>
+      <c r="U80" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T80" s="5">
-        <f t="shared" si="22"/>
-        <v>12.5</v>
-      </c>
-      <c r="U80" s="5">
-        <f t="shared" si="20"/>
         <v>12.5</v>
       </c>
       <c r="V80" s="5">
@@ -9341,10 +9564,13 @@
       </c>
       <c r="AF80" s="5"/>
       <c r="AG80" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH80" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH80" s="5">
+        <f t="shared" si="25"/>
+        <v>7.8363636363636369</v>
+      </c>
       <c r="AI80" s="5"/>
       <c r="AJ80" s="5"/>
       <c r="AK80" s="5"/>
@@ -9388,7 +9614,7 @@
         <v>62</v>
       </c>
       <c r="L81" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M81" s="5"/>
@@ -9398,20 +9624,20 @@
       </c>
       <c r="P81" s="5"/>
       <c r="Q81" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.6</v>
       </c>
       <c r="R81" s="4"/>
       <c r="S81" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T81" s="5">
+        <f t="shared" si="23"/>
+        <v>33.015873015873019</v>
+      </c>
+      <c r="U81" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T81" s="5">
-        <f t="shared" si="22"/>
-        <v>33.015873015873019</v>
-      </c>
-      <c r="U81" s="5">
-        <f t="shared" si="20"/>
         <v>33.015873015873019</v>
       </c>
       <c r="V81" s="5">
@@ -9448,10 +9674,13 @@
         <v>102</v>
       </c>
       <c r="AG81" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH81" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH81" s="5">
+        <f t="shared" si="25"/>
+        <v>17.018181818181816</v>
+      </c>
       <c r="AI81" s="5"/>
       <c r="AJ81" s="5"/>
       <c r="AK81" s="5"/>
@@ -9493,7 +9722,7 @@
         <v>40</v>
       </c>
       <c r="L82" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M82" s="5"/>
@@ -9503,23 +9732,23 @@
       </c>
       <c r="P82" s="5"/>
       <c r="Q82" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="R82" s="4">
-        <f t="shared" ref="R82:R83" si="25">11*Q82-P82-F82-O82</f>
+        <f t="shared" ref="R82:R83" si="27">11*Q82-P82-F82-O82</f>
         <v>60</v>
       </c>
       <c r="S82" s="4">
+        <f t="shared" si="22"/>
+        <v>60</v>
+      </c>
+      <c r="T82" s="5">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="U82" s="5">
         <f t="shared" si="21"/>
-        <v>60</v>
-      </c>
-      <c r="T82" s="5">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="U82" s="5">
-        <f t="shared" si="20"/>
         <v>2.4285714285714284</v>
       </c>
       <c r="V82" s="5">
@@ -9554,10 +9783,13 @@
       </c>
       <c r="AF82" s="5"/>
       <c r="AG82" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>21</v>
       </c>
-      <c r="AH82" s="5"/>
+      <c r="AH82" s="5">
+        <f t="shared" si="25"/>
+        <v>5.327272727272728</v>
+      </c>
       <c r="AI82" s="5"/>
       <c r="AJ82" s="5"/>
       <c r="AK82" s="5"/>
@@ -9599,7 +9831,7 @@
         <v>44</v>
       </c>
       <c r="L83" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3</v>
       </c>
       <c r="M83" s="5"/>
@@ -9609,23 +9841,23 @@
       </c>
       <c r="P83" s="5"/>
       <c r="Q83" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="R83" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>81.199999999999989</v>
       </c>
       <c r="S83" s="4">
+        <f t="shared" si="22"/>
+        <v>81.199999999999989</v>
+      </c>
+      <c r="T83" s="5">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="U83" s="5">
         <f t="shared" si="21"/>
-        <v>81.199999999999989</v>
-      </c>
-      <c r="T83" s="5">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="U83" s="5">
-        <f t="shared" si="20"/>
         <v>1.0975609756097562</v>
       </c>
       <c r="V83" s="5">
@@ -9660,10 +9892,13 @@
       </c>
       <c r="AF83" s="5"/>
       <c r="AG83" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>28</v>
       </c>
-      <c r="AH83" s="5"/>
+      <c r="AH83" s="5">
+        <f t="shared" si="25"/>
+        <v>4.6000000000000005</v>
+      </c>
       <c r="AI83" s="5"/>
       <c r="AJ83" s="5"/>
       <c r="AK83" s="5"/>
@@ -9695,7 +9930,7 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M84" s="10"/>
@@ -9705,20 +9940,20 @@
       </c>
       <c r="P84" s="10"/>
       <c r="Q84" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R84" s="12"/>
       <c r="S84" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U84" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T84" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U84" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" s="10">
@@ -9755,10 +9990,13 @@
         <v>46</v>
       </c>
       <c r="AG84" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH84" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH84" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI84" s="5"/>
       <c r="AJ84" s="5"/>
       <c r="AK84" s="5"/>
@@ -9790,7 +10028,7 @@
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -9800,20 +10038,20 @@
       </c>
       <c r="P85" s="10"/>
       <c r="Q85" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R85" s="12"/>
       <c r="S85" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T85" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U85" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T85" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U85" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" s="10">
@@ -9850,10 +10088,13 @@
         <v>46</v>
       </c>
       <c r="AG85" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH85" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH85" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI85" s="5"/>
       <c r="AJ85" s="5"/>
       <c r="AK85" s="5"/>
@@ -9893,7 +10134,7 @@
         <v>77</v>
       </c>
       <c r="L86" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-77</v>
       </c>
       <c r="M86" s="10"/>
@@ -9903,20 +10144,20 @@
       </c>
       <c r="P86" s="10"/>
       <c r="Q86" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R86" s="12"/>
       <c r="S86" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T86" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U86" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T86" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U86" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" s="10">
@@ -9951,10 +10192,13 @@
       </c>
       <c r="AF86" s="10"/>
       <c r="AG86" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH86" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH86" s="5">
+        <f t="shared" si="25"/>
+        <v>13.090909090909092</v>
+      </c>
       <c r="AI86" s="5"/>
       <c r="AJ86" s="5"/>
       <c r="AK86" s="5"/>
@@ -9998,7 +10242,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.1470000000000002</v>
       </c>
       <c r="M87" s="5"/>
@@ -10008,20 +10252,20 @@
       </c>
       <c r="P87" s="5"/>
       <c r="Q87" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.1494</v>
       </c>
       <c r="R87" s="4"/>
       <c r="S87" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T87" s="5">
+        <f t="shared" si="23"/>
+        <v>31.185836088393945</v>
+      </c>
+      <c r="U87" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T87" s="5">
-        <f t="shared" si="22"/>
-        <v>31.185836088393945</v>
-      </c>
-      <c r="U87" s="5">
-        <f t="shared" si="20"/>
         <v>31.185836088393945</v>
       </c>
       <c r="V87" s="5">
@@ -10058,10 +10302,13 @@
         <v>102</v>
       </c>
       <c r="AG87" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH87" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH87" s="5">
+        <f t="shared" si="25"/>
+        <v>1.4403454545454546</v>
+      </c>
       <c r="AI87" s="5"/>
       <c r="AJ87" s="5"/>
       <c r="AK87" s="5"/>
@@ -10105,7 +10352,7 @@
         <v>201.3</v>
       </c>
       <c r="L88" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.373999999999995</v>
       </c>
       <c r="M88" s="5"/>
@@ -10115,20 +10362,20 @@
       </c>
       <c r="P88" s="5"/>
       <c r="Q88" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>42.334800000000001</v>
       </c>
       <c r="R88" s="4"/>
       <c r="S88" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T88" s="5">
+        <f t="shared" si="23"/>
+        <v>13.606394739079903</v>
+      </c>
+      <c r="U88" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T88" s="5">
-        <f t="shared" si="22"/>
-        <v>13.606394739079903</v>
-      </c>
-      <c r="U88" s="5">
-        <f t="shared" si="20"/>
         <v>13.606394739079903</v>
       </c>
       <c r="V88" s="5">
@@ -10163,10 +10410,13 @@
       </c>
       <c r="AF88" s="5"/>
       <c r="AG88" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH88" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH88" s="5">
+        <f t="shared" si="25"/>
+        <v>54.722981818181822</v>
+      </c>
       <c r="AI88" s="5"/>
       <c r="AJ88" s="5"/>
       <c r="AK88" s="5"/>
@@ -10198,7 +10448,7 @@
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
       <c r="L89" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M89" s="10"/>
@@ -10208,20 +10458,20 @@
       </c>
       <c r="P89" s="10"/>
       <c r="Q89" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R89" s="12"/>
       <c r="S89" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T89" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U89" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T89" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U89" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V89" s="10">
@@ -10258,10 +10508,13 @@
         <v>46</v>
       </c>
       <c r="AG89" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH89" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH89" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI89" s="5"/>
       <c r="AJ89" s="5"/>
       <c r="AK89" s="5"/>
@@ -10305,7 +10558,7 @@
         <v>1760</v>
       </c>
       <c r="L90" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-12.025000000000091</v>
       </c>
       <c r="M90" s="5"/>
@@ -10315,20 +10568,20 @@
       </c>
       <c r="P90" s="5"/>
       <c r="Q90" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>349.59499999999997</v>
       </c>
       <c r="R90" s="4"/>
       <c r="S90" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T90" s="5">
+        <f t="shared" si="23"/>
+        <v>14.035739990331665</v>
+      </c>
+      <c r="U90" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T90" s="5">
-        <f t="shared" si="22"/>
-        <v>14.035739990331665</v>
-      </c>
-      <c r="U90" s="5">
-        <f t="shared" si="20"/>
         <v>14.035739990331665</v>
       </c>
       <c r="V90" s="5">
@@ -10363,10 +10616,13 @@
       </c>
       <c r="AF90" s="5"/>
       <c r="AG90" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH90" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH90" s="5">
+        <f t="shared" si="25"/>
+        <v>326.32443636363638</v>
+      </c>
       <c r="AI90" s="5"/>
       <c r="AJ90" s="5"/>
       <c r="AK90" s="5"/>
@@ -10410,7 +10666,7 @@
         <v>1722.5</v>
       </c>
       <c r="L91" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-44.2349999999999</v>
       </c>
       <c r="M91" s="5"/>
@@ -10422,20 +10678,20 @@
         <v>1000</v>
       </c>
       <c r="Q91" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>335.65300000000002</v>
       </c>
       <c r="R91" s="4"/>
       <c r="S91" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T91" s="5">
+        <f t="shared" si="23"/>
+        <v>15.047297655614576</v>
+      </c>
+      <c r="U91" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T91" s="5">
-        <f t="shared" si="22"/>
-        <v>15.047297655614576</v>
-      </c>
-      <c r="U91" s="5">
-        <f t="shared" si="20"/>
         <v>15.047297655614576</v>
       </c>
       <c r="V91" s="5">
@@ -10470,10 +10726,13 @@
       </c>
       <c r="AF91" s="5"/>
       <c r="AG91" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH91" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH91" s="5">
+        <f t="shared" si="25"/>
+        <v>339.98578181818181</v>
+      </c>
       <c r="AI91" s="5"/>
       <c r="AJ91" s="5"/>
       <c r="AK91" s="5"/>
@@ -10517,7 +10776,7 @@
         <v>2707.5</v>
       </c>
       <c r="L92" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-18.030999999999949</v>
       </c>
       <c r="M92" s="5"/>
@@ -10529,20 +10788,20 @@
         <v>2400</v>
       </c>
       <c r="Q92" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>537.89380000000006</v>
       </c>
       <c r="R92" s="4"/>
       <c r="S92" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T92" s="5">
+        <f t="shared" si="23"/>
+        <v>13.786285694313637</v>
+      </c>
+      <c r="U92" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T92" s="5">
-        <f t="shared" si="22"/>
-        <v>13.786285694313637</v>
-      </c>
-      <c r="U92" s="5">
-        <f t="shared" si="20"/>
         <v>13.786285694313637</v>
       </c>
       <c r="V92" s="5">
@@ -10577,10 +10836,13 @@
       </c>
       <c r="AF92" s="5"/>
       <c r="AG92" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH92" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH92" s="5">
+        <f t="shared" si="25"/>
+        <v>533.10816363636377</v>
+      </c>
       <c r="AI92" s="5"/>
       <c r="AJ92" s="5"/>
       <c r="AK92" s="5"/>
@@ -10612,7 +10874,7 @@
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M93" s="10"/>
@@ -10622,20 +10884,20 @@
       </c>
       <c r="P93" s="10"/>
       <c r="Q93" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R93" s="12"/>
       <c r="S93" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T93" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U93" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T93" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U93" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" s="10">
@@ -10672,10 +10934,13 @@
         <v>46</v>
       </c>
       <c r="AG93" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH93" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH93" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI93" s="5"/>
       <c r="AJ93" s="5"/>
       <c r="AK93" s="5"/>
@@ -10719,7 +10984,7 @@
         <v>42</v>
       </c>
       <c r="L94" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-39</v>
       </c>
       <c r="M94" s="5"/>
@@ -10729,20 +10994,20 @@
       </c>
       <c r="P94" s="5"/>
       <c r="Q94" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.6</v>
       </c>
       <c r="R94" s="4"/>
       <c r="S94" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T94" s="5">
+        <f t="shared" si="23"/>
+        <v>593.33333333333337</v>
+      </c>
+      <c r="U94" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T94" s="5">
-        <f t="shared" si="22"/>
-        <v>593.33333333333337</v>
-      </c>
-      <c r="U94" s="5">
-        <f t="shared" si="20"/>
         <v>593.33333333333337</v>
       </c>
       <c r="V94" s="5">
@@ -10777,10 +11042,13 @@
       </c>
       <c r="AF94" s="5"/>
       <c r="AG94" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH94" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH94" s="5">
+        <f t="shared" si="25"/>
+        <v>22.945454545454545</v>
+      </c>
       <c r="AI94" s="5"/>
       <c r="AJ94" s="5"/>
       <c r="AK94" s="5"/>
@@ -10812,7 +11080,7 @@
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M95" s="10"/>
@@ -10822,20 +11090,20 @@
       </c>
       <c r="P95" s="10"/>
       <c r="Q95" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R95" s="12"/>
       <c r="S95" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T95" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U95" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T95" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U95" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" s="10">
@@ -10872,10 +11140,13 @@
         <v>46</v>
       </c>
       <c r="AG95" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH95" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH95" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI95" s="5"/>
       <c r="AJ95" s="5"/>
       <c r="AK95" s="5"/>
@@ -10917,7 +11188,7 @@
         <v>83</v>
       </c>
       <c r="L96" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="M96" s="5"/>
@@ -10927,23 +11198,23 @@
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17</v>
       </c>
       <c r="R96" s="4">
-        <f t="shared" ref="R96:R98" si="26">11*Q96-P96-F96-O96</f>
+        <f t="shared" ref="R96:R98" si="28">11*Q96-P96-F96-O96</f>
         <v>67</v>
       </c>
       <c r="S96" s="4">
+        <f t="shared" si="22"/>
+        <v>67</v>
+      </c>
+      <c r="T96" s="5">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="U96" s="5">
         <f t="shared" si="21"/>
-        <v>67</v>
-      </c>
-      <c r="T96" s="5">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="U96" s="5">
-        <f t="shared" si="20"/>
         <v>7.0588235294117645</v>
       </c>
       <c r="V96" s="5">
@@ -10978,10 +11249,13 @@
       </c>
       <c r="AF96" s="5"/>
       <c r="AG96" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5</v>
       </c>
-      <c r="AH96" s="5"/>
+      <c r="AH96" s="5">
+        <f t="shared" si="25"/>
+        <v>11.618181818181819</v>
+      </c>
       <c r="AI96" s="5"/>
       <c r="AJ96" s="5"/>
       <c r="AK96" s="5"/>
@@ -11021,7 +11295,7 @@
         <v>63</v>
       </c>
       <c r="L97" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-7</v>
       </c>
       <c r="M97" s="5"/>
@@ -11031,23 +11305,23 @@
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.2</v>
       </c>
       <c r="R97" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>123.19999999999999</v>
       </c>
       <c r="S97" s="4">
+        <f t="shared" si="22"/>
+        <v>123.19999999999999</v>
+      </c>
+      <c r="T97" s="5">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="U97" s="5">
         <f t="shared" si="21"/>
-        <v>123.19999999999999</v>
-      </c>
-      <c r="T97" s="5">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="U97" s="5">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V97" s="5">
@@ -11082,10 +11356,13 @@
       </c>
       <c r="AF97" s="5"/>
       <c r="AG97" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9</v>
       </c>
-      <c r="AH97" s="5"/>
+      <c r="AH97" s="5">
+        <f t="shared" si="25"/>
+        <v>6.8</v>
+      </c>
       <c r="AI97" s="5"/>
       <c r="AJ97" s="5"/>
       <c r="AK97" s="5"/>
@@ -11129,7 +11406,7 @@
         <v>64</v>
       </c>
       <c r="L98" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="M98" s="5"/>
@@ -11139,23 +11416,23 @@
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.6</v>
       </c>
       <c r="R98" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>11.599999999999994</v>
       </c>
       <c r="S98" s="4">
+        <f t="shared" si="22"/>
+        <v>11.599999999999994</v>
+      </c>
+      <c r="T98" s="5">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="U98" s="5">
         <f t="shared" si="21"/>
-        <v>11.599999999999994</v>
-      </c>
-      <c r="T98" s="5">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="U98" s="5">
-        <f t="shared" si="20"/>
         <v>10.079365079365079</v>
       </c>
       <c r="V98" s="5">
@@ -11190,10 +11467,13 @@
       </c>
       <c r="AF98" s="5"/>
       <c r="AG98" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="AH98" s="5"/>
+      <c r="AH98" s="5">
+        <f t="shared" si="25"/>
+        <v>9.836363636363636</v>
+      </c>
       <c r="AI98" s="5"/>
       <c r="AJ98" s="5"/>
       <c r="AK98" s="5"/>
@@ -11235,7 +11515,7 @@
         <v>82</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-12</v>
       </c>
       <c r="M99" s="10"/>
@@ -11245,20 +11525,20 @@
       </c>
       <c r="P99" s="10"/>
       <c r="Q99" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="R99" s="12"/>
       <c r="S99" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T99" s="5">
+        <f t="shared" si="23"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U99" s="10">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T99" s="5">
-        <f t="shared" si="22"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="U99" s="10">
-        <f t="shared" si="20"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="V99" s="10">
@@ -11293,10 +11573,13 @@
       </c>
       <c r="AF99" s="10"/>
       <c r="AG99" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH99" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH99" s="5">
+        <f t="shared" si="25"/>
+        <v>12.654545454545454</v>
+      </c>
       <c r="AI99" s="5"/>
       <c r="AJ99" s="5"/>
       <c r="AK99" s="5"/>
@@ -11336,7 +11619,7 @@
         <v>28</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-37</v>
       </c>
       <c r="M100" s="10"/>
@@ -11346,20 +11629,20 @@
       </c>
       <c r="P100" s="10"/>
       <c r="Q100" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1.8</v>
       </c>
       <c r="R100" s="12"/>
       <c r="S100" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T100" s="5">
+        <f t="shared" si="23"/>
+        <v>-0.55555555555555558</v>
+      </c>
+      <c r="U100" s="10">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T100" s="5">
-        <f t="shared" si="22"/>
-        <v>-0.55555555555555558</v>
-      </c>
-      <c r="U100" s="10">
-        <f t="shared" si="20"/>
         <v>-0.55555555555555558</v>
       </c>
       <c r="V100" s="10">
@@ -11396,10 +11679,13 @@
         <v>138</v>
       </c>
       <c r="AG100" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH100" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH100" s="5">
+        <f t="shared" si="25"/>
+        <v>4.6181818181818182</v>
+      </c>
       <c r="AI100" s="5"/>
       <c r="AJ100" s="5"/>
       <c r="AK100" s="5"/>
@@ -11431,7 +11717,7 @@
       <c r="J101" s="10"/>
       <c r="K101" s="10"/>
       <c r="L101" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M101" s="10"/>
@@ -11441,20 +11727,20 @@
       </c>
       <c r="P101" s="10"/>
       <c r="Q101" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R101" s="12"/>
       <c r="S101" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="T101" s="5" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U101" s="10" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T101" s="5" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U101" s="10" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V101" s="10">
@@ -11491,10 +11777,13 @@
         <v>46</v>
       </c>
       <c r="AG101" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH101" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH101" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI101" s="5"/>
       <c r="AJ101" s="5"/>
       <c r="AK101" s="5"/>
@@ -11534,7 +11823,7 @@
         <v>1</v>
       </c>
       <c r="L102" s="10">
-        <f t="shared" ref="L102:L133" si="27">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="29">E102-K102</f>
         <v>-1.272</v>
       </c>
       <c r="M102" s="10"/>
@@ -11544,20 +11833,20 @@
       </c>
       <c r="P102" s="10"/>
       <c r="Q102" s="10">
-        <f t="shared" ref="Q102:Q133" si="28">E102/5</f>
+        <f t="shared" ref="Q102:Q133" si="30">E102/5</f>
         <v>-5.4400000000000004E-2</v>
       </c>
       <c r="R102" s="12"/>
       <c r="S102" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T102" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>58.327205882352935</v>
       </c>
       <c r="U102" s="10">
-        <f t="shared" ref="U102:U133" si="29">(F102+O102+P102)/Q102</f>
+        <f t="shared" ref="U102:U133" si="31">(F102+O102+P102)/Q102</f>
         <v>58.327205882352935</v>
       </c>
       <c r="V102" s="10">
@@ -11594,10 +11883,13 @@
         <v>46</v>
       </c>
       <c r="AG102" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH102" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH102" s="5">
+        <f t="shared" si="25"/>
+        <v>5.6937090909090911</v>
+      </c>
       <c r="AI102" s="5"/>
       <c r="AJ102" s="5"/>
       <c r="AK102" s="5"/>
@@ -11629,7 +11921,7 @@
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
       <c r="L103" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M103" s="10"/>
@@ -11639,20 +11931,20 @@
       </c>
       <c r="P103" s="10"/>
       <c r="Q103" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R103" s="12"/>
       <c r="S103" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T103" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U103" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" s="10">
@@ -11689,10 +11981,13 @@
         <v>46</v>
       </c>
       <c r="AG103" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH103" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH103" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI103" s="5"/>
       <c r="AJ103" s="5"/>
       <c r="AK103" s="5"/>
@@ -11724,7 +12019,7 @@
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
       <c r="L104" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M104" s="10"/>
@@ -11734,20 +12029,20 @@
       </c>
       <c r="P104" s="10"/>
       <c r="Q104" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R104" s="12"/>
       <c r="S104" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T104" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U104" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" s="10">
@@ -11784,10 +12079,13 @@
         <v>46</v>
       </c>
       <c r="AG104" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH104" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH104" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI104" s="5"/>
       <c r="AJ104" s="5"/>
       <c r="AK104" s="5"/>
@@ -11829,7 +12127,7 @@
         <v>99</v>
       </c>
       <c r="L105" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="M105" s="5"/>
@@ -11839,23 +12137,23 @@
       </c>
       <c r="P105" s="5"/>
       <c r="Q105" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="R105" s="4">
-        <f t="shared" ref="R105:R106" si="30">11*Q105-P105-F105-O105</f>
+        <f t="shared" ref="R105:R106" si="32">11*Q105-P105-F105-O105</f>
         <v>116.80000000000001</v>
       </c>
       <c r="S105" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>116.80000000000001</v>
       </c>
       <c r="T105" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U105" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>5.1599999999999993</v>
       </c>
       <c r="V105" s="5">
@@ -11890,10 +12188,13 @@
       </c>
       <c r="AF105" s="5"/>
       <c r="AG105" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9</v>
       </c>
-      <c r="AH105" s="5"/>
+      <c r="AH105" s="5">
+        <f t="shared" si="25"/>
+        <v>12.127272727272727</v>
+      </c>
       <c r="AI105" s="5"/>
       <c r="AJ105" s="5"/>
       <c r="AK105" s="5"/>
@@ -11935,7 +12236,7 @@
         <v>97</v>
       </c>
       <c r="L106" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3</v>
       </c>
       <c r="M106" s="5"/>
@@ -11945,23 +12246,23 @@
       </c>
       <c r="P106" s="5"/>
       <c r="Q106" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="R106" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>123</v>
       </c>
       <c r="S106" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>123</v>
       </c>
       <c r="T106" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U106" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.8499999999999996</v>
       </c>
       <c r="V106" s="5">
@@ -11996,10 +12297,13 @@
       </c>
       <c r="AF106" s="5"/>
       <c r="AG106" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
-      <c r="AH106" s="5"/>
+      <c r="AH106" s="5">
+        <f t="shared" si="25"/>
+        <v>15.581818181818182</v>
+      </c>
       <c r="AI106" s="5"/>
       <c r="AJ106" s="5"/>
       <c r="AK106" s="5"/>
@@ -12031,7 +12335,7 @@
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
       <c r="L107" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M107" s="10"/>
@@ -12041,20 +12345,20 @@
       </c>
       <c r="P107" s="10"/>
       <c r="Q107" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R107" s="12"/>
       <c r="S107" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T107" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" s="10">
@@ -12091,10 +12395,13 @@
         <v>46</v>
       </c>
       <c r="AG107" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH107" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH107" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI107" s="5"/>
       <c r="AJ107" s="5"/>
       <c r="AK107" s="5"/>
@@ -12138,7 +12445,7 @@
         <v>185.5</v>
       </c>
       <c r="L108" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.1870000000000118</v>
       </c>
       <c r="M108" s="5"/>
@@ -12148,23 +12455,23 @@
       </c>
       <c r="P108" s="5"/>
       <c r="Q108" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>38.737400000000001</v>
       </c>
       <c r="R108" s="4">
-        <f t="shared" ref="R108:R110" si="31">11*Q108-P108-F108-O108</f>
+        <f t="shared" ref="R108:R110" si="33">11*Q108-P108-F108-O108</f>
         <v>48.398600000000101</v>
       </c>
       <c r="S108" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>48.398600000000101</v>
       </c>
       <c r="T108" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U108" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>9.7505976136756694</v>
       </c>
       <c r="V108" s="5">
@@ -12199,10 +12506,13 @@
       </c>
       <c r="AF108" s="5"/>
       <c r="AG108" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>48</v>
       </c>
-      <c r="AH108" s="5"/>
+      <c r="AH108" s="5">
+        <f t="shared" si="25"/>
+        <v>42.659672727272728</v>
+      </c>
       <c r="AI108" s="5"/>
       <c r="AJ108" s="5"/>
       <c r="AK108" s="5"/>
@@ -12246,7 +12556,7 @@
         <v>176.4</v>
       </c>
       <c r="L109" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.1490000000000009</v>
       </c>
       <c r="M109" s="5"/>
@@ -12256,20 +12566,20 @@
       </c>
       <c r="P109" s="5"/>
       <c r="Q109" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>35.509799999999998</v>
       </c>
       <c r="R109" s="4"/>
       <c r="S109" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T109" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.154419343392529</v>
       </c>
       <c r="U109" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>12.154419343392529</v>
       </c>
       <c r="V109" s="5">
@@ -12304,10 +12614,13 @@
       </c>
       <c r="AF109" s="5"/>
       <c r="AG109" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH109" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH109" s="5">
+        <f t="shared" si="25"/>
+        <v>46.205690909090904</v>
+      </c>
       <c r="AI109" s="5"/>
       <c r="AJ109" s="5"/>
       <c r="AK109" s="5"/>
@@ -12351,7 +12664,7 @@
         <v>257</v>
       </c>
       <c r="L110" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.63900000000001</v>
       </c>
       <c r="M110" s="5"/>
@@ -12361,23 +12674,23 @@
       </c>
       <c r="P110" s="5"/>
       <c r="Q110" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>51.527799999999999</v>
       </c>
       <c r="R110" s="4">
+        <f t="shared" si="33"/>
+        <v>50.367120000000057</v>
+      </c>
+      <c r="S110" s="4">
+        <f t="shared" si="22"/>
+        <v>50.367120000000057</v>
+      </c>
+      <c r="T110" s="5">
+        <f t="shared" si="23"/>
+        <v>11.000000000000002</v>
+      </c>
+      <c r="U110" s="5">
         <f t="shared" si="31"/>
-        <v>50.367120000000057</v>
-      </c>
-      <c r="S110" s="4">
-        <f t="shared" si="21"/>
-        <v>50.367120000000057</v>
-      </c>
-      <c r="T110" s="5">
-        <f t="shared" si="22"/>
-        <v>11.000000000000002</v>
-      </c>
-      <c r="U110" s="5">
-        <f t="shared" si="29"/>
         <v>10.02252531643113</v>
       </c>
       <c r="V110" s="5">
@@ -12412,10 +12725,13 @@
       </c>
       <c r="AF110" s="5"/>
       <c r="AG110" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>50</v>
       </c>
-      <c r="AH110" s="5"/>
+      <c r="AH110" s="5">
+        <f t="shared" si="25"/>
+        <v>56.79698181818182</v>
+      </c>
       <c r="AI110" s="5"/>
       <c r="AJ110" s="5"/>
       <c r="AK110" s="5"/>
@@ -12447,7 +12763,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
       <c r="L111" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M111" s="10"/>
@@ -12457,20 +12773,20 @@
       </c>
       <c r="P111" s="10"/>
       <c r="Q111" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R111" s="12"/>
       <c r="S111" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T111" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U111" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V111" s="10">
@@ -12507,10 +12823,13 @@
         <v>46</v>
       </c>
       <c r="AG111" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH111" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH111" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI111" s="5"/>
       <c r="AJ111" s="5"/>
       <c r="AK111" s="5"/>
@@ -12542,7 +12861,7 @@
       <c r="J112" s="10"/>
       <c r="K112" s="10"/>
       <c r="L112" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M112" s="10"/>
@@ -12552,20 +12871,20 @@
       </c>
       <c r="P112" s="10"/>
       <c r="Q112" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R112" s="12"/>
       <c r="S112" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T112" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U112" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V112" s="10">
@@ -12602,10 +12921,13 @@
         <v>46</v>
       </c>
       <c r="AG112" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH112" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH112" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI112" s="5"/>
       <c r="AJ112" s="5"/>
       <c r="AK112" s="5"/>
@@ -12647,7 +12969,7 @@
         <v>286</v>
       </c>
       <c r="L113" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-4</v>
       </c>
       <c r="M113" s="5"/>
@@ -12657,23 +12979,23 @@
       </c>
       <c r="P113" s="5"/>
       <c r="Q113" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>56.4</v>
       </c>
       <c r="R113" s="4">
-        <f t="shared" ref="R113:R115" si="32">11*Q113-P113-F113-O113</f>
+        <f t="shared" ref="R113:R115" si="34">11*Q113-P113-F113-O113</f>
         <v>557.4</v>
       </c>
       <c r="S113" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>557.4</v>
       </c>
       <c r="T113" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U113" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.1170212765957448</v>
       </c>
       <c r="V113" s="5">
@@ -12708,10 +13030,13 @@
       </c>
       <c r="AF113" s="5"/>
       <c r="AG113" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>156</v>
       </c>
-      <c r="AH113" s="5"/>
+      <c r="AH113" s="5">
+        <f t="shared" si="25"/>
+        <v>21.290909090909093</v>
+      </c>
       <c r="AI113" s="5"/>
       <c r="AJ113" s="5"/>
       <c r="AK113" s="5"/>
@@ -12755,7 +13080,7 @@
         <v>224</v>
       </c>
       <c r="L114" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="M114" s="5"/>
@@ -12765,23 +13090,23 @@
       </c>
       <c r="P114" s="5"/>
       <c r="Q114" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>45.8</v>
       </c>
       <c r="R114" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>313.79999999999995</v>
       </c>
       <c r="S114" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>313.79999999999995</v>
       </c>
       <c r="T114" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U114" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.1484716157205241</v>
       </c>
       <c r="V114" s="5">
@@ -12816,10 +13141,13 @@
       </c>
       <c r="AF114" s="5"/>
       <c r="AG114" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>88</v>
       </c>
-      <c r="AH114" s="5"/>
+      <c r="AH114" s="5">
+        <f t="shared" si="25"/>
+        <v>30.581818181818186</v>
+      </c>
       <c r="AI114" s="5"/>
       <c r="AJ114" s="5"/>
       <c r="AK114" s="5"/>
@@ -12863,7 +13191,7 @@
         <v>209</v>
       </c>
       <c r="L115" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>6</v>
       </c>
       <c r="M115" s="5"/>
@@ -12873,23 +13201,23 @@
       </c>
       <c r="P115" s="5"/>
       <c r="Q115" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
       <c r="R115" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>157.4</v>
       </c>
       <c r="S115" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>157.4</v>
       </c>
       <c r="T115" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U115" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.3395348837209307</v>
       </c>
       <c r="V115" s="5">
@@ -12924,10 +13252,13 @@
       </c>
       <c r="AF115" s="5"/>
       <c r="AG115" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>44</v>
       </c>
-      <c r="AH115" s="5"/>
+      <c r="AH115" s="5">
+        <f t="shared" si="25"/>
+        <v>36.490909090909099</v>
+      </c>
       <c r="AI115" s="5"/>
       <c r="AJ115" s="5"/>
       <c r="AK115" s="5"/>
@@ -12959,7 +13290,7 @@
       <c r="J116" s="10"/>
       <c r="K116" s="10"/>
       <c r="L116" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M116" s="10"/>
@@ -12969,20 +13300,20 @@
       </c>
       <c r="P116" s="10"/>
       <c r="Q116" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R116" s="12"/>
       <c r="S116" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T116" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U116" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V116" s="10">
@@ -13019,10 +13350,13 @@
         <v>46</v>
       </c>
       <c r="AG116" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH116" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH116" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI116" s="5"/>
       <c r="AJ116" s="5"/>
       <c r="AK116" s="5"/>
@@ -13066,7 +13400,7 @@
         <v>116.6</v>
       </c>
       <c r="L117" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-24.36399999999999</v>
       </c>
       <c r="M117" s="5"/>
@@ -13076,7 +13410,7 @@
       </c>
       <c r="P117" s="5"/>
       <c r="Q117" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>18.447200000000002</v>
       </c>
       <c r="R117" s="4">
@@ -13084,15 +13418,15 @@
         <v>126.8922</v>
       </c>
       <c r="S117" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>126.8922</v>
       </c>
       <c r="T117" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10.999999999999998</v>
       </c>
       <c r="U117" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.1213300663515327</v>
       </c>
       <c r="V117" s="5">
@@ -13127,10 +13461,13 @@
       </c>
       <c r="AF117" s="5"/>
       <c r="AG117" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>127</v>
       </c>
-      <c r="AH117" s="5"/>
+      <c r="AH117" s="5">
+        <f t="shared" si="25"/>
+        <v>17.548036363636363</v>
+      </c>
       <c r="AI117" s="5"/>
       <c r="AJ117" s="5"/>
       <c r="AK117" s="5"/>
@@ -13174,7 +13511,7 @@
         <v>66.5</v>
       </c>
       <c r="L118" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-16.694000000000003</v>
       </c>
       <c r="M118" s="5"/>
@@ -13184,20 +13521,20 @@
       </c>
       <c r="P118" s="5"/>
       <c r="Q118" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>9.9611999999999998</v>
       </c>
       <c r="R118" s="4"/>
       <c r="S118" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T118" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15.016263100831226</v>
       </c>
       <c r="U118" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15.016263100831226</v>
       </c>
       <c r="V118" s="5">
@@ -13232,10 +13569,13 @@
       </c>
       <c r="AF118" s="5"/>
       <c r="AG118" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH118" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH118" s="5">
+        <f t="shared" si="25"/>
+        <v>11.796618181818182</v>
+      </c>
       <c r="AI118" s="5"/>
       <c r="AJ118" s="5"/>
       <c r="AK118" s="5"/>
@@ -13267,7 +13607,7 @@
       <c r="J119" s="10"/>
       <c r="K119" s="10"/>
       <c r="L119" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M119" s="10"/>
@@ -13277,20 +13617,20 @@
       </c>
       <c r="P119" s="10"/>
       <c r="Q119" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R119" s="12"/>
       <c r="S119" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T119" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U119" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V119" s="10">
@@ -13327,10 +13667,13 @@
         <v>46</v>
       </c>
       <c r="AG119" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH119" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH119" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI119" s="5"/>
       <c r="AJ119" s="5"/>
       <c r="AK119" s="5"/>
@@ -13362,7 +13705,7 @@
       <c r="J120" s="10"/>
       <c r="K120" s="10"/>
       <c r="L120" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M120" s="10"/>
@@ -13372,20 +13715,20 @@
       </c>
       <c r="P120" s="10"/>
       <c r="Q120" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R120" s="12"/>
       <c r="S120" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T120" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U120" s="10" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V120" s="10">
@@ -13422,10 +13765,13 @@
         <v>46</v>
       </c>
       <c r="AG120" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH120" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH120" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI120" s="5"/>
       <c r="AJ120" s="5"/>
       <c r="AK120" s="5"/>
@@ -13469,7 +13815,7 @@
         <v>95.1</v>
       </c>
       <c r="L121" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>6.9520000000000124</v>
       </c>
       <c r="M121" s="5"/>
@@ -13479,20 +13825,20 @@
       </c>
       <c r="P121" s="5"/>
       <c r="Q121" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>20.410400000000003</v>
       </c>
       <c r="R121" s="4"/>
       <c r="S121" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T121" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.144034413828242</v>
       </c>
       <c r="U121" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.144034413828242</v>
       </c>
       <c r="V121" s="5">
@@ -13527,10 +13873,13 @@
       </c>
       <c r="AF121" s="5"/>
       <c r="AG121" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH121" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH121" s="5">
+        <f t="shared" si="25"/>
+        <v>11.28</v>
+      </c>
       <c r="AI121" s="5"/>
       <c r="AJ121" s="5"/>
       <c r="AK121" s="5"/>
@@ -13574,7 +13923,7 @@
         <v>184.1</v>
       </c>
       <c r="L122" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-1.1949999999999932</v>
       </c>
       <c r="M122" s="5"/>
@@ -13584,20 +13933,20 @@
       </c>
       <c r="P122" s="5"/>
       <c r="Q122" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>36.581000000000003</v>
       </c>
       <c r="R122" s="4"/>
       <c r="S122" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T122" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.930329952707686</v>
       </c>
       <c r="U122" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.930329952707686</v>
       </c>
       <c r="V122" s="5">
@@ -13632,10 +13981,13 @@
       </c>
       <c r="AF122" s="5"/>
       <c r="AG122" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH122" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH122" s="5">
+        <f t="shared" si="25"/>
+        <v>36.645127272727279</v>
+      </c>
       <c r="AI122" s="5"/>
       <c r="AJ122" s="5"/>
       <c r="AK122" s="5"/>
@@ -13679,7 +14031,7 @@
         <v>52.5</v>
       </c>
       <c r="L123" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>6.4209999999999994</v>
       </c>
       <c r="M123" s="5"/>
@@ -13689,20 +14041,20 @@
       </c>
       <c r="P123" s="5"/>
       <c r="Q123" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>11.7842</v>
       </c>
       <c r="R123" s="4"/>
       <c r="S123" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T123" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15.619558391744878</v>
       </c>
       <c r="U123" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15.619558391744878</v>
       </c>
       <c r="V123" s="5">
@@ -13737,10 +14089,13 @@
       </c>
       <c r="AF123" s="5"/>
       <c r="AG123" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH123" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH123" s="5">
+        <f t="shared" si="25"/>
+        <v>11.759618181818183</v>
+      </c>
       <c r="AI123" s="5"/>
       <c r="AJ123" s="5"/>
       <c r="AK123" s="5"/>
@@ -13784,7 +14139,7 @@
         <v>1025</v>
       </c>
       <c r="L124" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-13.979000000000042</v>
       </c>
       <c r="M124" s="5"/>
@@ -13796,20 +14151,20 @@
         <v>200</v>
       </c>
       <c r="Q124" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>202.20419999999999</v>
       </c>
       <c r="R124" s="4"/>
       <c r="S124" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T124" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.389634834489099</v>
       </c>
       <c r="U124" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.389634834489099</v>
       </c>
       <c r="V124" s="5">
@@ -13844,10 +14199,13 @@
       </c>
       <c r="AF124" s="5"/>
       <c r="AG124" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH124" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH124" s="5">
+        <f t="shared" si="25"/>
+        <v>129.60990909090907</v>
+      </c>
       <c r="AI124" s="5"/>
       <c r="AJ124" s="5"/>
       <c r="AK124" s="5"/>
@@ -13889,7 +14247,7 @@
         <v>165</v>
       </c>
       <c r="L125" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M125" s="5"/>
@@ -13899,22 +14257,22 @@
       </c>
       <c r="P125" s="5"/>
       <c r="Q125" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>33</v>
       </c>
       <c r="R125" s="4">
-        <f t="shared" ref="R125:R128" si="33">11*Q125-P125-F125-O125</f>
+        <f t="shared" ref="R125:R128" si="35">11*Q125-P125-F125-O125</f>
         <v>327</v>
       </c>
       <c r="S125" s="4">
         <v>500</v>
       </c>
       <c r="T125" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.242424242424242</v>
       </c>
       <c r="U125" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.0909090909090908</v>
       </c>
       <c r="V125" s="5">
@@ -13951,10 +14309,13 @@
         <v>176</v>
       </c>
       <c r="AG125" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>125</v>
       </c>
-      <c r="AH125" s="5"/>
+      <c r="AH125" s="5">
+        <f t="shared" si="25"/>
+        <v>3.9636363636363638</v>
+      </c>
       <c r="AI125" s="5"/>
       <c r="AJ125" s="5"/>
       <c r="AK125" s="5"/>
@@ -13998,7 +14359,7 @@
         <v>107</v>
       </c>
       <c r="L126" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="M126" s="5"/>
@@ -14008,22 +14369,22 @@
       </c>
       <c r="P126" s="5"/>
       <c r="Q126" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>22.4</v>
       </c>
       <c r="R126" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>154.39999999999998</v>
       </c>
       <c r="S126" s="4">
         <v>500</v>
       </c>
       <c r="T126" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>26.428571428571431</v>
       </c>
       <c r="U126" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.1071428571428577</v>
       </c>
       <c r="V126" s="5">
@@ -14060,10 +14421,13 @@
         <v>176</v>
       </c>
       <c r="AG126" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>163</v>
       </c>
-      <c r="AH126" s="5"/>
+      <c r="AH126" s="5">
+        <f t="shared" si="25"/>
+        <v>2.3272727272727272</v>
+      </c>
       <c r="AI126" s="5"/>
       <c r="AJ126" s="5"/>
       <c r="AK126" s="5"/>
@@ -14105,7 +14469,7 @@
         <v>147</v>
       </c>
       <c r="L127" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M127" s="5"/>
@@ -14115,22 +14479,22 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>29.4</v>
       </c>
       <c r="R127" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>271.39999999999998</v>
       </c>
       <c r="S127" s="4">
         <v>500</v>
       </c>
       <c r="T127" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18.775510204081634</v>
       </c>
       <c r="U127" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.7687074829931975</v>
       </c>
       <c r="V127" s="5">
@@ -14167,10 +14531,13 @@
         <v>176</v>
       </c>
       <c r="AG127" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>125</v>
       </c>
-      <c r="AH127" s="5"/>
+      <c r="AH127" s="5">
+        <f t="shared" si="25"/>
+        <v>3.3272727272727276</v>
+      </c>
       <c r="AI127" s="5"/>
       <c r="AJ127" s="5"/>
       <c r="AK127" s="5"/>
@@ -14212,7 +14579,7 @@
         <v>146</v>
       </c>
       <c r="L128" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-70</v>
       </c>
       <c r="M128" s="5"/>
@@ -14222,23 +14589,23 @@
       </c>
       <c r="P128" s="5"/>
       <c r="Q128" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15.2</v>
       </c>
       <c r="R128" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>167.2</v>
       </c>
       <c r="S128" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>167.2</v>
       </c>
       <c r="T128" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U128" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="V128" s="5">
@@ -14273,10 +14640,13 @@
       </c>
       <c r="AF128" s="5"/>
       <c r="AG128" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>50</v>
       </c>
-      <c r="AH128" s="5"/>
+      <c r="AH128" s="5">
+        <f t="shared" si="25"/>
+        <v>41.909090909090907</v>
+      </c>
       <c r="AI128" s="5"/>
       <c r="AJ128" s="5"/>
       <c r="AK128" s="5"/>
@@ -14320,7 +14690,7 @@
         <v>133</v>
       </c>
       <c r="L129" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-126</v>
       </c>
       <c r="M129" s="5"/>
@@ -14330,20 +14700,20 @@
       </c>
       <c r="P129" s="5"/>
       <c r="Q129" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1.4</v>
       </c>
       <c r="R129" s="4"/>
       <c r="S129" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T129" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>17.142857142857142</v>
       </c>
       <c r="U129" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>17.142857142857142</v>
       </c>
       <c r="V129" s="5">
@@ -14380,10 +14750,13 @@
         <v>168</v>
       </c>
       <c r="AG129" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH129" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH129" s="5">
+        <f t="shared" si="25"/>
+        <v>2.127272727272727</v>
+      </c>
       <c r="AI129" s="5"/>
       <c r="AJ129" s="5"/>
       <c r="AK129" s="5"/>
@@ -14427,7 +14800,7 @@
         <v>16.45</v>
       </c>
       <c r="L130" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-4.2399999999999984</v>
       </c>
       <c r="M130" s="5"/>
@@ -14437,20 +14810,20 @@
       </c>
       <c r="P130" s="5"/>
       <c r="Q130" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2.4420000000000002</v>
       </c>
       <c r="R130" s="4"/>
       <c r="S130" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T130" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>21.176085176085177</v>
       </c>
       <c r="U130" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>21.176085176085177</v>
       </c>
       <c r="V130" s="5">
@@ -14485,10 +14858,13 @@
       </c>
       <c r="AF130" s="5"/>
       <c r="AG130" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH130" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH130" s="5">
+        <f t="shared" si="25"/>
+        <v>1.9653272727272728</v>
+      </c>
       <c r="AI130" s="5"/>
       <c r="AJ130" s="5"/>
       <c r="AK130" s="5"/>
@@ -14530,7 +14906,7 @@
         <v>211</v>
       </c>
       <c r="L131" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-13</v>
       </c>
       <c r="M131" s="5"/>
@@ -14540,22 +14916,22 @@
       </c>
       <c r="P131" s="5"/>
       <c r="Q131" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>39.6</v>
       </c>
       <c r="R131" s="17">
         <v>80</v>
       </c>
       <c r="S131" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>80</v>
       </c>
       <c r="T131" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.7121212121212119</v>
       </c>
       <c r="U131" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.6919191919191918</v>
       </c>
       <c r="V131" s="5">
@@ -14590,10 +14966,13 @@
       </c>
       <c r="AF131" s="5"/>
       <c r="AG131" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
-      <c r="AH131" s="5"/>
+      <c r="AH131" s="5">
+        <f t="shared" si="25"/>
+        <v>24.090909090909097</v>
+      </c>
       <c r="AI131" s="5"/>
       <c r="AJ131" s="5"/>
       <c r="AK131" s="5"/>
@@ -14637,7 +15016,7 @@
         <v>70</v>
       </c>
       <c r="L132" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="M132" s="5"/>
@@ -14647,23 +15026,23 @@
       </c>
       <c r="P132" s="5"/>
       <c r="Q132" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="R132" s="4">
-        <f t="shared" ref="R132" si="34">11*Q132-P132-F132-O132</f>
+        <f t="shared" ref="R132" si="36">11*Q132-P132-F132-O132</f>
         <v>32</v>
       </c>
       <c r="S132" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>32</v>
       </c>
       <c r="T132" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="U132" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>8.8666666666666671</v>
       </c>
       <c r="V132" s="5">
@@ -14698,10 +15077,13 @@
       </c>
       <c r="AF132" s="5"/>
       <c r="AG132" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
-      <c r="AH132" s="5"/>
+      <c r="AH132" s="5">
+        <f t="shared" si="25"/>
+        <v>10.345454545454546</v>
+      </c>
       <c r="AI132" s="5"/>
       <c r="AJ132" s="5"/>
       <c r="AK132" s="5"/>
@@ -14743,7 +15125,7 @@
         <v>6</v>
       </c>
       <c r="L133" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="M133" s="10"/>
@@ -14751,20 +15133,20 @@
       <c r="O133" s="10"/>
       <c r="P133" s="10"/>
       <c r="Q133" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.6</v>
       </c>
       <c r="R133" s="12"/>
       <c r="S133" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="T133" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>78.333333333333343</v>
       </c>
       <c r="U133" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>78.333333333333343</v>
       </c>
       <c r="V133" s="10">
@@ -14799,10 +15181,13 @@
       </c>
       <c r="AF133" s="10"/>
       <c r="AG133" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH133" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH133" s="5">
+        <f t="shared" si="25"/>
+        <v>5.4545454545454543E-2</v>
+      </c>
       <c r="AI133" s="5"/>
       <c r="AJ133" s="5"/>
       <c r="AK133" s="5"/>
